--- a/data/trans_orig/P5702-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P5702-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de recibir ayuda en asuntos relacionados con mi casa en 2007</t>
+          <t>Población según la frecuencia de recibir ayuda en asuntos relacionados con mi casa en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>400076</t>
+          <t>396753</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>460683</t>
+          <t>460588</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>38,78%</t>
+          <t>38,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>44,65%</t>
+          <t>44,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>438385</t>
+          <t>436108</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>508629</t>
+          <t>505079</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>33,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>38,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>855501</t>
+          <t>859873</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>945684</t>
+          <t>952090</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>36,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>40,57%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>268279</t>
+          <t>267150</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>323489</t>
+          <t>322994</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>31,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>314790</t>
+          <t>315421</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>381124</t>
+          <t>378464</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>599752</t>
+          <t>603416</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>685326</t>
+          <t>682871</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>29,1%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>174086</t>
+          <t>174378</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>222993</t>
+          <t>223592</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>231681</t>
+          <t>232835</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289119</t>
+          <t>287427</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>421736</t>
+          <t>420809</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>500987</t>
+          <t>497834</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,21%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>73549</t>
+          <t>74728</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>114133</t>
+          <t>111756</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>170864</t>
+          <t>170422</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>222584</t>
+          <t>221921</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>258393</t>
+          <t>258021</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>318869</t>
+          <t>319228</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,6%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10518</t>
+          <t>10112</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>30202</t>
+          <t>28678</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>26110</t>
+          <t>26728</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>50608</t>
+          <t>51201</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>41144</t>
+          <t>40762</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>72572</t>
+          <t>72663</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>853454</t>
+          <t>851648</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>933860</t>
+          <t>932793</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>50,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>55,15%</t>
+          <t>55,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>705692</t>
+          <t>705918</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>781708</t>
+          <t>784388</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>44,45%</t>
+          <t>44,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>49,24%</t>
+          <t>49,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1581953</t>
+          <t>1583580</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1698142</t>
+          <t>1694309</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,21%</t>
+          <t>48,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>51,76%</t>
+          <t>51,64%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>441170</t>
+          <t>440365</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>511166</t>
+          <t>515581</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>377544</t>
+          <t>378972</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>449508</t>
+          <t>447918</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>837268</t>
+          <t>841807</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>936960</t>
+          <t>936302</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>28,54%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>204245</t>
+          <t>201271</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>260727</t>
+          <t>258620</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>214517</t>
+          <t>215503</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>277374</t>
+          <t>272920</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>434246</t>
+          <t>434643</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>514566</t>
+          <t>513428</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,65%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>49308</t>
+          <t>48103</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>82396</t>
+          <t>81060</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>129054</t>
+          <t>130731</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>178262</t>
+          <t>176717</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>189824</t>
+          <t>191599</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>249218</t>
+          <t>248076</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,56%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>20160</t>
+          <t>20280</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>43661</t>
+          <t>42887</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>23119</t>
+          <t>23503</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>46911</t>
+          <t>47832</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>48363</t>
+          <t>48845</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>81059</t>
+          <t>80578</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>266043</t>
+          <t>265325</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>311184</t>
+          <t>312881</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>48,25%</t>
+          <t>48,12%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>56,43%</t>
+          <t>56,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>247748</t>
+          <t>248908</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>292904</t>
+          <t>292450</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>52,0%</t>
+          <t>52,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>61,48%</t>
+          <t>61,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>525105</t>
+          <t>525635</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>588378</t>
+          <t>590211</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>51,09%</t>
+          <t>51,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>57,25%</t>
+          <t>57,42%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>141853</t>
+          <t>143205</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>185258</t>
+          <t>186135</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>25,97%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,6%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>95597</t>
+          <t>96384</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>132693</t>
+          <t>134164</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>250801</t>
+          <t>249493</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>308581</t>
+          <t>307298</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>29,9%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>59608</t>
+          <t>59497</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>92143</t>
+          <t>92851</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>42944</t>
+          <t>42892</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>71670</t>
+          <t>71386</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>107849</t>
+          <t>108888</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>151577</t>
+          <t>156339</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>15,21%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9667</t>
+          <t>8849</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>26221</t>
+          <t>25462</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>18607</t>
+          <t>19364</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>41551</t>
+          <t>39997</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>32072</t>
+          <t>31231</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>57851</t>
+          <t>59472</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,79%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4390</t>
+          <t>3944</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>18296</t>
+          <t>19337</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2803</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>16822</t>
+          <t>16479</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>10302</t>
+          <t>9853</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>29375</t>
+          <t>28729</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1558102</t>
+          <t>1552239</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1679440</t>
+          <t>1671541</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>47,55%</t>
+          <t>47,37%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>51,26%</t>
+          <t>51,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1424769</t>
+          <t>1435877</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1548813</t>
+          <t>1545112</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>42,16%</t>
+          <t>42,49%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>45,83%</t>
+          <t>45,72%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3014489</t>
+          <t>3022105</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3179413</t>
+          <t>3187241</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>45,29%</t>
+          <t>45,41%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>47,77%</t>
+          <t>47,89%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>882115</t>
+          <t>884795</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>983114</t>
+          <t>985371</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>825791</t>
+          <t>824918</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>931020</t>
+          <t>922343</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1739609</t>
+          <t>1737396</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1886414</t>
+          <t>1881853</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,27%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>463830</t>
+          <t>461265</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>547856</t>
+          <t>544628</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>514660</t>
+          <t>516506</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>602312</t>
+          <t>604491</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1000470</t>
+          <t>1003431</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1123185</t>
+          <t>1125701</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,91%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>145971</t>
+          <t>144930</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>198125</t>
+          <t>197410</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>338938</t>
+          <t>341288</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>414674</t>
+          <t>419477</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>502714</t>
+          <t>501855</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>595261</t>
+          <t>595201</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>43007</t>
+          <t>42747</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>75324</t>
+          <t>76429</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>62614</t>
+          <t>62588</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>98484</t>
+          <t>97855</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>112189</t>
+          <t>114849</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>159392</t>
+          <t>162711</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,44%</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3497,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de recibir ayuda en asuntos relacionados con mi casa en 2012</t>
+          <t>Población según la frecuencia de recibir ayuda en asuntos relacionados con mi casa en 2012 (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>427503</t>
+          <t>427027</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>491929</t>
+          <t>491434</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>44,08%</t>
+          <t>44,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>50,72%</t>
+          <t>50,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>504334</t>
+          <t>501172</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>582362</t>
+          <t>574436</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>37,73%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,57%</t>
+          <t>42,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>950824</t>
+          <t>943450</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1046245</t>
+          <t>1042760</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>41,22%</t>
+          <t>40,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>45,36%</t>
+          <t>45,21%</t>
         </is>
       </c>
     </row>
@@ -3805,12 +3805,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>244251</t>
+          <t>248437</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>304193</t>
+          <t>303299</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3820,12 +3820,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,37%</t>
+          <t>31,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>366476</t>
+          <t>368324</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>437597</t>
+          <t>436474</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3855,12 +3855,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>32,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>634504</t>
+          <t>635308</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>723450</t>
+          <t>724163</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3890,12 +3890,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>31,4%</t>
         </is>
       </c>
     </row>
@@ -3918,12 +3918,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>130759</t>
+          <t>131111</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>177204</t>
+          <t>180360</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3933,12 +3933,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>181277</t>
+          <t>178249</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>233693</t>
+          <t>232252</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3968,12 +3968,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>319500</t>
+          <t>323452</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>394544</t>
+          <t>393166</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4003,12 +4003,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>17,05%</t>
         </is>
       </c>
     </row>
@@ -4031,12 +4031,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>55172</t>
+          <t>53584</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>89683</t>
+          <t>86854</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4046,12 +4046,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>100246</t>
+          <t>103776</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>146083</t>
+          <t>146323</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4081,12 +4081,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>167656</t>
+          <t>171033</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>223116</t>
+          <t>224682</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4116,12 +4116,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,74%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9415</t>
+          <t>9632</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>27211</t>
+          <t>28573</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>51438</t>
+          <t>51224</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>83630</t>
+          <t>84457</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>65573</t>
+          <t>65412</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>101287</t>
+          <t>101640</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,41%</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1002872</t>
+          <t>998653</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1095199</t>
+          <t>1091762</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>51,12%</t>
+          <t>50,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>55,83%</t>
+          <t>55,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>733051</t>
+          <t>735277</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>817208</t>
+          <t>818824</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>41,73%</t>
+          <t>41,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,52%</t>
+          <t>46,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1758297</t>
+          <t>1758284</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1879344</t>
+          <t>1887994</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>50,54%</t>
+          <t>50,77%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>469116</t>
+          <t>473852</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>553117</t>
+          <t>551633</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>437762</t>
+          <t>437014</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>511598</t>
+          <t>512331</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>933203</t>
+          <t>929960</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1043108</t>
+          <t>1036351</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>27,87%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>216088</t>
+          <t>213032</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>274625</t>
+          <t>273162</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>220034</t>
+          <t>219577</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>283190</t>
+          <t>280556</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>453461</t>
+          <t>452606</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>537623</t>
+          <t>536526</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,43%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>87694</t>
+          <t>87409</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>131359</t>
+          <t>130699</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>138097</t>
+          <t>137427</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>187744</t>
+          <t>186706</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>238417</t>
+          <t>239162</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>302042</t>
+          <t>302218</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,13%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>36732</t>
+          <t>35116</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>69658</t>
+          <t>68233</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>77000</t>
+          <t>77372</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>120109</t>
+          <t>116449</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>126944</t>
+          <t>124265</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>179508</t>
+          <t>173166</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,66%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>253891</t>
+          <t>259245</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>302986</t>
+          <t>302024</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>53,0%</t>
+          <t>54,11%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>63,24%</t>
+          <t>63,04%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>225517</t>
+          <t>227419</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>273702</t>
+          <t>272366</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>49,17%</t>
+          <t>49,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>59,68%</t>
+          <t>59,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>495824</t>
+          <t>498359</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>559998</t>
+          <t>560957</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>52,88%</t>
+          <t>53,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>59,72%</t>
+          <t>59,82%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>90602</t>
+          <t>92432</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>132099</t>
+          <t>130523</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>105460</t>
+          <t>105813</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>146661</t>
+          <t>145721</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>31,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>208625</t>
+          <t>206668</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>265635</t>
+          <t>263024</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>28,05%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>39295</t>
+          <t>40418</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>70525</t>
+          <t>69442</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>32597</t>
+          <t>33243</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>58402</t>
+          <t>58583</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>80038</t>
+          <t>79788</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>120733</t>
+          <t>120712</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,87%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14535</t>
+          <t>15234</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>34491</t>
+          <t>35419</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>18674</t>
+          <t>19015</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>40678</t>
+          <t>39764</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>38324</t>
+          <t>38651</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>66973</t>
+          <t>67222</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,17%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5188</t>
+          <t>5715</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>21350</t>
+          <t>21904</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5854</t>
+          <t>5928</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>18753</t>
+          <t>19084</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>14160</t>
+          <t>14120</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>34320</t>
+          <t>35136</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,75%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1723024</t>
+          <t>1723780</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1840887</t>
+          <t>1845324</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>50,52%</t>
+          <t>50,54%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>53,98%</t>
+          <t>54,11%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1503153</t>
+          <t>1500815</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1622239</t>
+          <t>1626575</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>42,32%</t>
+          <t>42,25%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>45,67%</t>
+          <t>45,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3253798</t>
+          <t>3261921</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3433953</t>
+          <t>3436495</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>46,73%</t>
+          <t>46,85%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>49,32%</t>
+          <t>49,36%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>849269</t>
+          <t>843332</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>954632</t>
+          <t>948068</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>948874</t>
+          <t>945634</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1059983</t>
+          <t>1057551</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1821670</t>
+          <t>1816584</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1977876</t>
+          <t>1971612</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>28,32%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>413556</t>
+          <t>410839</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>493200</t>
+          <t>496744</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>459057</t>
+          <t>460045</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>542596</t>
+          <t>547577</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>885151</t>
+          <t>891262</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1008856</t>
+          <t>1005973</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,45%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>173250</t>
+          <t>173255</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>228996</t>
+          <t>234473</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>279964</t>
+          <t>277228</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>347879</t>
+          <t>350629</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>471888</t>
+          <t>471465</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>559740</t>
+          <t>562939</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,09%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>60964</t>
+          <t>60849</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>99143</t>
+          <t>98979</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>148551</t>
+          <t>150488</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>203903</t>
+          <t>204243</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>222210</t>
+          <t>220440</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>289521</t>
+          <t>288648</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,15%</t>
         </is>
       </c>
     </row>
@@ -6456,7 +6456,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de recibir ayuda en asuntos relacionados con mi casa en 2016</t>
+          <t>Población según la frecuencia de recibir ayuda en asuntos relacionados con mi casa en 2016 (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6651,12 +6651,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>279537</t>
+          <t>278470</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>331998</t>
+          <t>331099</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6666,12 +6666,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>37,06%</t>
+          <t>36,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>44,01%</t>
+          <t>43,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6686,12 +6686,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>309518</t>
+          <t>309445</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>370632</t>
+          <t>373187</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6706,7 +6706,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,35%</t>
+          <t>37,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6721,12 +6721,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>603730</t>
+          <t>604843</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>683932</t>
+          <t>686420</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>34,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,16%</t>
+          <t>39,3%</t>
         </is>
       </c>
     </row>
@@ -6764,12 +6764,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>218590</t>
+          <t>219412</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>270519</t>
+          <t>268847</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6779,12 +6779,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,86%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6799,12 +6799,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>272334</t>
+          <t>274709</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>332111</t>
+          <t>332915</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>33,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>504142</t>
+          <t>508331</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>586690</t>
+          <t>585643</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,59%</t>
+          <t>33,53%</t>
         </is>
       </c>
     </row>
@@ -6877,12 +6877,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>127573</t>
+          <t>128031</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>171448</t>
+          <t>172984</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6892,12 +6892,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>184035</t>
+          <t>184914</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>239524</t>
+          <t>238309</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6927,47 +6927,47 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
+          <t>18,64%</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>24,02%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>337</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>361120</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>324020</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>396618</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>20,68%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
           <t>18,55%</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>24,14%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>337</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>361120</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>328182</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>396057</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>20,68%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>18,79%</t>
-        </is>
-      </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,71%</t>
         </is>
       </c>
     </row>
@@ -6990,12 +6990,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>37390</t>
+          <t>38824</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>63456</t>
+          <t>65073</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7005,12 +7005,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>84107</t>
+          <t>83012</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>124918</t>
+          <t>126269</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7040,12 +7040,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>128621</t>
+          <t>130456</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>176104</t>
+          <t>178711</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7075,12 +7075,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,23%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2790</t>
+          <t>2749</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13630</t>
+          <t>13503</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>24998</t>
+          <t>25932</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>50666</t>
+          <t>51121</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>30926</t>
+          <t>31308</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>57147</t>
+          <t>58424</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,34%</t>
         </is>
       </c>
     </row>
@@ -7333,12 +7333,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>821240</t>
+          <t>822811</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>909148</t>
+          <t>916027</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7348,12 +7348,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>39,64%</t>
+          <t>39,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>43,88%</t>
+          <t>44,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7368,12 +7368,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>695179</t>
+          <t>692574</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>782400</t>
+          <t>780629</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7383,12 +7383,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>34,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,42%</t>
+          <t>39,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7403,12 +7403,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1537818</t>
+          <t>1537089</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1662777</t>
+          <t>1663782</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7418,12 +7418,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>37,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>40,99%</t>
+          <t>41,01%</t>
         </is>
       </c>
     </row>
@@ -7446,12 +7446,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>684339</t>
+          <t>682213</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>770984</t>
+          <t>772832</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7461,47 +7461,47 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
+          <t>32,93%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>37,3%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>699573</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>655630</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>741466</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>35,25%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
           <t>33,03%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>37,21%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>667</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>699573</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>654310</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>740418</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>35,25%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>32,97%</t>
-        </is>
-      </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1367132</t>
+          <t>1363799</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1487553</t>
+          <t>1492464</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7531,12 +7531,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>33,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>36,67%</t>
+          <t>36,79%</t>
         </is>
       </c>
     </row>
@@ -7559,12 +7559,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>299980</t>
+          <t>302013</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>372407</t>
+          <t>367311</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7574,12 +7574,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>310145</t>
+          <t>309928</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>375104</t>
+          <t>382506</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>632397</t>
+          <t>630757</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>723961</t>
+          <t>725971</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,9%</t>
         </is>
       </c>
     </row>
@@ -7672,12 +7672,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>82815</t>
+          <t>82704</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>122719</t>
+          <t>121767</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7687,12 +7687,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7707,12 +7707,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>117231</t>
+          <t>120819</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>165154</t>
+          <t>165378</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7722,12 +7722,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7742,12 +7742,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>212168</t>
+          <t>210827</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>274048</t>
+          <t>271643</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,7%</t>
         </is>
       </c>
     </row>
@@ -7785,12 +7785,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>30888</t>
+          <t>32475</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>58750</t>
+          <t>59871</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7800,12 +7800,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7820,12 +7820,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>50214</t>
+          <t>51475</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>82825</t>
+          <t>82951</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7835,12 +7835,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>90531</t>
+          <t>89518</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>133249</t>
+          <t>133924</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,3%</t>
         </is>
       </c>
     </row>
@@ -8015,12 +8015,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>250027</t>
+          <t>250981</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>297962</t>
+          <t>302839</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8030,12 +8030,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>45,79%</t>
+          <t>45,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>54,57%</t>
+          <t>55,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8050,12 +8050,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>243510</t>
+          <t>243089</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>290077</t>
+          <t>290499</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8065,12 +8065,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>44,42%</t>
+          <t>44,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>52,91%</t>
+          <t>52,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>509478</t>
+          <t>510523</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>579484</t>
+          <t>579176</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>46,56%</t>
+          <t>46,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>52,96%</t>
+          <t>52,93%</t>
         </is>
       </c>
     </row>
@@ -8128,12 +8128,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>146263</t>
+          <t>141013</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>193431</t>
+          <t>185333</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8143,12 +8143,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>33,94%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8163,12 +8163,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>133175</t>
+          <t>134137</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>171757</t>
+          <t>176290</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8178,12 +8178,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>32,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8198,12 +8198,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>286991</t>
+          <t>284342</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>347131</t>
+          <t>345868</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>31,61%</t>
         </is>
       </c>
     </row>
@@ -8241,12 +8241,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>63985</t>
+          <t>63902</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>99064</t>
+          <t>100488</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8256,12 +8256,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8276,12 +8276,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>57254</t>
+          <t>56974</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>88467</t>
+          <t>87967</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8291,12 +8291,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8311,12 +8311,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>130450</t>
+          <t>128751</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>176934</t>
+          <t>175665</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8326,12 +8326,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,05%</t>
         </is>
       </c>
     </row>
@@ -8354,12 +8354,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11118</t>
+          <t>11282</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>29279</t>
+          <t>28711</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8369,12 +8369,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8389,12 +8389,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>21854</t>
+          <t>21509</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>44572</t>
+          <t>45437</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8404,12 +8404,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8424,12 +8424,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>36139</t>
+          <t>37179</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>64707</t>
+          <t>65328</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8439,12 +8439,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,97%</t>
         </is>
       </c>
     </row>
@@ -8467,12 +8467,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3302</t>
+          <t>3031</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>17073</t>
+          <t>16460</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8482,12 +8482,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8502,12 +8502,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>14707</t>
+          <t>14755</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>36263</t>
+          <t>34877</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8517,12 +8517,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8537,12 +8537,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>21290</t>
+          <t>21146</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>44391</t>
+          <t>45403</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8552,12 +8552,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,15%</t>
         </is>
       </c>
     </row>
@@ -8697,12 +8697,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1389716</t>
+          <t>1386447</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1504680</t>
+          <t>1505598</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8712,12 +8712,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>41,21%</t>
+          <t>41,11%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>44,62%</t>
+          <t>44,65%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8732,12 +8732,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1285317</t>
+          <t>1286393</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1398530</t>
+          <t>1403990</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8747,12 +8747,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>36,49%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>39,83%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8767,12 +8767,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2704240</t>
+          <t>2709238</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2870213</t>
+          <t>2882479</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8782,12 +8782,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>39,21%</t>
+          <t>39,28%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>41,61%</t>
+          <t>41,79%</t>
         </is>
       </c>
     </row>
@@ -8810,12 +8810,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1081171</t>
+          <t>1077911</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1192565</t>
+          <t>1190259</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8825,12 +8825,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>35,3%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8845,12 +8845,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1097625</t>
+          <t>1099022</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1210090</t>
+          <t>1212959</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8860,12 +8860,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>34,33%</t>
+          <t>34,41%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8880,12 +8880,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2214507</t>
+          <t>2214990</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2366909</t>
+          <t>2376241</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8900,7 +8900,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>34,45%</t>
         </is>
       </c>
     </row>
@@ -8923,12 +8923,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>522207</t>
+          <t>519376</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>610369</t>
+          <t>609599</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8938,12 +8938,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8958,12 +8958,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>579259</t>
+          <t>579528</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>674599</t>
+          <t>668805</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8973,12 +8973,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8993,12 +8993,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1132348</t>
+          <t>1129556</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1257037</t>
+          <t>1258740</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9008,12 +9008,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,25%</t>
         </is>
       </c>
     </row>
@@ -9036,12 +9036,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>144279</t>
+          <t>144798</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>196135</t>
+          <t>196975</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9071,12 +9071,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>243488</t>
+          <t>240820</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>307432</t>
+          <t>307298</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9086,7 +9086,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>400583</t>
+          <t>400420</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>486830</t>
+          <t>482073</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9126,7 +9126,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,99%</t>
         </is>
       </c>
     </row>
@@ -9149,12 +9149,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>44638</t>
+          <t>44743</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>77163</t>
+          <t>78047</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9184,12 +9184,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>104453</t>
+          <t>105430</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>149307</t>
+          <t>148447</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9199,12 +9199,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>159210</t>
+          <t>159804</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>214084</t>
+          <t>216735</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -9415,7 +9415,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de recibir ayuda en asuntos relacionados con mi casa en 2023</t>
+          <t>Población según la frecuencia de recibir ayuda en asuntos relacionados con mi casa en 2023 (tasa de respuesta: 99,7%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9610,12 +9610,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>224559</t>
+          <t>222271</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>264355</t>
+          <t>264880</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9625,12 +9625,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>43,68%</t>
+          <t>43,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>51,42%</t>
+          <t>51,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9645,12 +9645,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>301226</t>
+          <t>302345</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>344515</t>
+          <t>342931</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9660,12 +9660,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>40,06%</t>
+          <t>40,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>45,81%</t>
+          <t>45,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9680,12 +9680,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>535974</t>
+          <t>538952</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>594083</t>
+          <t>595537</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9695,12 +9695,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>42,33%</t>
+          <t>42,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>46,92%</t>
+          <t>47,04%</t>
         </is>
       </c>
     </row>
@@ -9723,12 +9723,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>120792</t>
+          <t>122975</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>157572</t>
+          <t>161194</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9738,12 +9738,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9758,12 +9758,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>187423</t>
+          <t>189143</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>224819</t>
+          <t>226731</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9773,12 +9773,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>30,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9793,12 +9793,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>321620</t>
+          <t>320710</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>373185</t>
+          <t>372318</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9808,12 +9808,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>29,41%</t>
         </is>
       </c>
     </row>
@@ -9836,12 +9836,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>62487</t>
+          <t>63008</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>89715</t>
+          <t>92225</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9851,12 +9851,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9871,12 +9871,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>110544</t>
+          <t>107990</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>140013</t>
+          <t>139168</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9886,12 +9886,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9906,12 +9906,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>181528</t>
+          <t>181001</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>221347</t>
+          <t>223264</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9921,12 +9921,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,63%</t>
         </is>
       </c>
     </row>
@@ -9949,12 +9949,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26017</t>
+          <t>25885</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>46616</t>
+          <t>45848</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9964,12 +9964,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9984,12 +9984,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>55153</t>
+          <t>54878</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>76293</t>
+          <t>77667</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9999,12 +9999,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10019,12 +10019,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>86075</t>
+          <t>85428</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>116469</t>
+          <t>114141</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,02%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12998</t>
+          <t>12670</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>28860</t>
+          <t>28477</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>22459</t>
+          <t>22532</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>52777</t>
+          <t>53024</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>39652</t>
+          <t>40438</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>72688</t>
+          <t>68706</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,43%</t>
         </is>
       </c>
     </row>
@@ -10292,12 +10292,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1333855</t>
+          <t>1334845</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1696524</t>
+          <t>1724382</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10307,12 +10307,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>58,39%</t>
+          <t>58,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>74,27%</t>
+          <t>75,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10327,12 +10327,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1085630</t>
+          <t>1082683</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1239696</t>
+          <t>1273329</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10342,12 +10342,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>53,49%</t>
+          <t>53,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>61,08%</t>
+          <t>62,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10362,12 +10362,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2454297</t>
+          <t>2458415</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2876676</t>
+          <t>2927984</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10377,12 +10377,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>56,89%</t>
+          <t>56,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>66,68%</t>
+          <t>67,87%</t>
         </is>
       </c>
     </row>
@@ -10405,12 +10405,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>372118</t>
+          <t>374799</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>614516</t>
+          <t>612420</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10420,12 +10420,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10440,12 +10440,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>485791</t>
+          <t>479528</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>592801</t>
+          <t>591711</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10455,12 +10455,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10475,12 +10475,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>902049</t>
+          <t>877542</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1172138</t>
+          <t>1170222</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10490,12 +10490,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>27,13%</t>
         </is>
       </c>
     </row>
@@ -10518,12 +10518,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>138853</t>
+          <t>133076</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>242944</t>
+          <t>242044</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10533,12 +10533,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10553,12 +10553,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>171998</t>
+          <t>168058</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>223947</t>
+          <t>229905</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10568,12 +10568,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10588,12 +10588,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>330340</t>
+          <t>330345</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>449538</t>
+          <t>452714</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10608,7 +10608,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,49%</t>
         </is>
       </c>
     </row>
@@ -10631,12 +10631,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>44786</t>
+          <t>44345</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>82782</t>
+          <t>83424</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10646,12 +10646,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10666,12 +10666,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>82609</t>
+          <t>83785</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>120486</t>
+          <t>119374</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10681,12 +10681,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10701,12 +10701,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>133117</t>
+          <t>134681</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>190763</t>
+          <t>191420</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10716,12 +10716,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>21244</t>
+          <t>21166</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>45418</t>
+          <t>45760</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10764,7 +10764,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>32866</t>
+          <t>32014</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>55708</t>
+          <t>57171</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>59261</t>
+          <t>59937</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>94057</t>
+          <t>94553</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -10974,12 +10974,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>375968</t>
+          <t>371637</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>427872</t>
+          <t>427785</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10989,12 +10989,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>58,38%</t>
+          <t>57,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>66,44%</t>
+          <t>66,43%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11009,12 +11009,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>378534</t>
+          <t>375795</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>422215</t>
+          <t>419453</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11024,12 +11024,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>57,37%</t>
+          <t>56,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>63,99%</t>
+          <t>63,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>760229</t>
+          <t>767735</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>832756</t>
+          <t>836528</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>58,31%</t>
+          <t>58,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>63,87%</t>
+          <t>64,16%</t>
         </is>
       </c>
     </row>
@@ -11087,12 +11087,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>142021</t>
+          <t>139043</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>191514</t>
+          <t>193126</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11102,12 +11102,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11122,12 +11122,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>153012</t>
+          <t>153457</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>190426</t>
+          <t>190606</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>303819</t>
+          <t>304367</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>369600</t>
+          <t>369651</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11172,7 +11172,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -11200,12 +11200,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>32257</t>
+          <t>32194</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>57386</t>
+          <t>57415</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11215,12 +11215,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11235,12 +11235,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>33699</t>
+          <t>32275</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>56445</t>
+          <t>56312</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>72489</t>
+          <t>70828</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>105306</t>
+          <t>106911</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,2%</t>
         </is>
       </c>
     </row>
@@ -11313,12 +11313,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14823</t>
+          <t>14499</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>35962</t>
+          <t>35999</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11328,12 +11328,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11348,12 +11348,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>23124</t>
+          <t>23727</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>41452</t>
+          <t>42807</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11363,12 +11363,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11383,12 +11383,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>41817</t>
+          <t>41885</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>69937</t>
+          <t>69011</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11403,7 +11403,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,29%</t>
         </is>
       </c>
     </row>
@@ -11426,12 +11426,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5989</t>
+          <t>6251</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>20887</t>
+          <t>20883</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11441,7 +11441,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -11461,12 +11461,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>9218</t>
+          <t>9036</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>20229</t>
+          <t>21224</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11476,12 +11476,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11496,12 +11496,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>18564</t>
+          <t>18327</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>38103</t>
+          <t>37471</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11511,12 +11511,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,87%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1977652</t>
+          <t>1978965</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2387586</t>
+          <t>2428180</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>57,45%</t>
+          <t>57,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>69,36%</t>
+          <t>70,54%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1797931</t>
+          <t>1793211</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1973019</t>
+          <t>1966539</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>52,24%</t>
+          <t>52,11%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>57,33%</t>
+          <t>57,14%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3816944</t>
+          <t>3814007</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4329715</t>
+          <t>4329830</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11741,7 +11741,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>55,45%</t>
+          <t>55,4%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -11769,12 +11769,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>651904</t>
+          <t>620898</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>920022</t>
+          <t>913009</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11804,12 +11804,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>860524</t>
+          <t>862111</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>977297</t>
+          <t>982123</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1548079</t>
+          <t>1549167</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1867547</t>
+          <t>1866922</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>27,12%</t>
         </is>
       </c>
     </row>
@@ -11882,12 +11882,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>255018</t>
+          <t>251584</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>367417</t>
+          <t>367073</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11897,12 +11897,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11917,12 +11917,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>331105</t>
+          <t>327232</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>397310</t>
+          <t>402257</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>610175</t>
+          <t>605503</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>744514</t>
+          <t>747587</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,86%</t>
         </is>
       </c>
     </row>
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>92335</t>
+          <t>93912</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>148406</t>
+          <t>143740</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12010,12 +12010,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12030,12 +12030,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>172327</t>
+          <t>176020</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>221443</t>
+          <t>220811</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12045,12 +12045,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12065,12 +12065,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>276333</t>
+          <t>273990</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>355067</t>
+          <t>352472</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12080,12 +12080,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,12%</t>
         </is>
       </c>
     </row>
@@ -12108,12 +12108,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>47437</t>
+          <t>47549</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>82802</t>
+          <t>83040</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12143,12 +12143,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>73469</t>
+          <t>73517</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>114584</t>
+          <t>112631</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12158,12 +12158,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12178,12 +12178,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>129361</t>
+          <t>128892</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>181737</t>
+          <t>181378</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12193,12 +12193,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P5702-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P5702-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>396753</t>
+          <t>400292</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>460588</t>
+          <t>461533</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>38,46%</t>
+          <t>38,8%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>44,64%</t>
+          <t>44,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>436108</t>
+          <t>438319</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>505079</t>
+          <t>509156</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,16%</t>
+          <t>33,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>38,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>859873</t>
+          <t>853996</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>952090</t>
+          <t>947061</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>36,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,57%</t>
+          <t>40,35%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>267150</t>
+          <t>267522</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>322994</t>
+          <t>324652</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,31%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>315421</t>
+          <t>317528</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>378464</t>
+          <t>380502</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>603416</t>
+          <t>604775</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>682871</t>
+          <t>688592</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>29,34%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>174378</t>
+          <t>174990</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>223592</t>
+          <t>222698</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>232835</t>
+          <t>230552</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>287427</t>
+          <t>290432</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>420809</t>
+          <t>421842</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>497834</t>
+          <t>498719</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>21,25%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>74728</t>
+          <t>75187</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>111756</t>
+          <t>112919</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>170422</t>
+          <t>171595</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>221921</t>
+          <t>222864</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>258021</t>
+          <t>256524</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>319228</t>
+          <t>319764</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,63%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10112</t>
+          <t>10129</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>28678</t>
+          <t>30291</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>26728</t>
+          <t>26393</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>51201</t>
+          <t>51169</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,7 +1235,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>40762</t>
+          <t>42073</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>72663</t>
+          <t>71898</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>851648</t>
+          <t>853536</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>932793</t>
+          <t>942545</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>50,29%</t>
+          <t>50,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>55,08%</t>
+          <t>55,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>705918</t>
+          <t>705069</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>784388</t>
+          <t>781578</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>44,46%</t>
+          <t>44,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>49,4%</t>
+          <t>49,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1583580</t>
+          <t>1579412</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1694309</t>
+          <t>1699807</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,26%</t>
+          <t>48,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>51,64%</t>
+          <t>51,81%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>440365</t>
+          <t>436077</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>515581</t>
+          <t>511466</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,47 +1543,47 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
+          <t>25,75%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>30,2%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>408</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>412818</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>376432</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>446432</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
           <t>26,0%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>30,45%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>408</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>412818</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>378972</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>447918</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>26,0%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>841807</t>
+          <t>838006</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>936302</t>
+          <t>938520</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>28,6%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>201271</t>
+          <t>200788</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>258620</t>
+          <t>259284</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>215503</t>
+          <t>216298</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>272920</t>
+          <t>276566</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>434643</t>
+          <t>433231</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>513428</t>
+          <t>512713</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,63%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>48103</t>
+          <t>48564</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>81060</t>
+          <t>81163</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>130731</t>
+          <t>130965</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>176717</t>
+          <t>178183</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>191599</t>
+          <t>189472</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>248076</t>
+          <t>249242</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,6%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>20280</t>
+          <t>19413</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>42887</t>
+          <t>42893</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>23503</t>
+          <t>22919</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>47832</t>
+          <t>47686</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>48845</t>
+          <t>48005</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>80578</t>
+          <t>79741</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>265325</t>
+          <t>263097</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>312881</t>
+          <t>313164</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>48,12%</t>
+          <t>47,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>56,74%</t>
+          <t>56,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>248908</t>
+          <t>247844</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>292450</t>
+          <t>290426</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>52,25%</t>
+          <t>52,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>61,39%</t>
+          <t>60,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>525635</t>
+          <t>523111</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>590211</t>
+          <t>590920</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>51,14%</t>
+          <t>50,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>57,42%</t>
+          <t>57,49%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>143205</t>
+          <t>142626</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>186135</t>
+          <t>186497</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>96384</t>
+          <t>95673</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>134164</t>
+          <t>135570</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>249493</t>
+          <t>248364</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>307298</t>
+          <t>308563</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>30,02%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>59497</t>
+          <t>56765</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>92851</t>
+          <t>89322</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>42892</t>
+          <t>42925</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>71386</t>
+          <t>72174</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>108888</t>
+          <t>109019</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>156339</t>
+          <t>153265</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>14,91%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8849</t>
+          <t>9063</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>25462</t>
+          <t>25553</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>19364</t>
+          <t>19189</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>39997</t>
+          <t>40705</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>31231</t>
+          <t>32737</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>59472</t>
+          <t>60683</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,9%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3944</t>
+          <t>4208</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>19337</t>
+          <t>18311</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>3063</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>16479</t>
+          <t>17032</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>9853</t>
+          <t>9556</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>28729</t>
+          <t>29297</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1552239</t>
+          <t>1553434</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1671541</t>
+          <t>1670711</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>47,37%</t>
+          <t>47,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>51,02%</t>
+          <t>50,99%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1435877</t>
+          <t>1426542</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1545112</t>
+          <t>1537396</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>42,49%</t>
+          <t>42,22%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>45,72%</t>
+          <t>45,5%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3022105</t>
+          <t>3027477</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3187241</t>
+          <t>3189436</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>45,41%</t>
+          <t>45,49%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>47,89%</t>
+          <t>47,92%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>884795</t>
+          <t>884953</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>985371</t>
+          <t>989285</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>824918</t>
+          <t>829766</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>922343</t>
+          <t>931684</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1737396</t>
+          <t>1733925</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1881853</t>
+          <t>1885231</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>28,32%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>461265</t>
+          <t>461105</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>544628</t>
+          <t>541415</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>516506</t>
+          <t>520021</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>604491</t>
+          <t>601008</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1003431</t>
+          <t>1002327</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1125701</t>
+          <t>1124936</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,9%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>144930</t>
+          <t>147819</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>197410</t>
+          <t>198976</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>341288</t>
+          <t>339168</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>419477</t>
+          <t>414397</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>501855</t>
+          <t>503962</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>595201</t>
+          <t>594344</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,93%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>42747</t>
+          <t>42389</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>76429</t>
+          <t>75635</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>62588</t>
+          <t>63505</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>97855</t>
+          <t>99328</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>114849</t>
+          <t>115423</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>162711</t>
+          <t>164540</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,47%</t>
         </is>
       </c>
     </row>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>427027</t>
+          <t>424163</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>491434</t>
+          <t>489471</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>43,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>50,67%</t>
+          <t>50,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>501172</t>
+          <t>501648</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>574436</t>
+          <t>574125</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>37,49%</t>
+          <t>37,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,97%</t>
+          <t>42,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>943450</t>
+          <t>943844</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1042760</t>
+          <t>1039872</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>40,9%</t>
+          <t>40,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>45,21%</t>
+          <t>45,08%</t>
         </is>
       </c>
     </row>
@@ -3805,12 +3805,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>248437</t>
+          <t>246275</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>303299</t>
+          <t>303297</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3820,7 +3820,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>368324</t>
+          <t>369256</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>436474</t>
+          <t>439428</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3855,12 +3855,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>635308</t>
+          <t>635634</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>724163</t>
+          <t>721191</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3890,12 +3890,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>31,27%</t>
         </is>
       </c>
     </row>
@@ -3918,12 +3918,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>131111</t>
+          <t>129869</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>180360</t>
+          <t>177698</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3933,12 +3933,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>178249</t>
+          <t>179473</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>232252</t>
+          <t>232527</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3968,12 +3968,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>323452</t>
+          <t>322021</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>393166</t>
+          <t>391968</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4003,12 +4003,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>16,99%</t>
         </is>
       </c>
     </row>
@@ -4031,12 +4031,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>53584</t>
+          <t>54079</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>86854</t>
+          <t>86462</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4046,12 +4046,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>103776</t>
+          <t>103645</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>146323</t>
+          <t>147424</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4081,12 +4081,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>171033</t>
+          <t>165517</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>224682</t>
+          <t>222934</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4116,12 +4116,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,67%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9632</t>
+          <t>9770</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>28573</t>
+          <t>26642</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>51224</t>
+          <t>51877</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>84457</t>
+          <t>83379</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>65412</t>
+          <t>65792</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>101640</t>
+          <t>102807</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>998653</t>
+          <t>996983</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1091762</t>
+          <t>1091820</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>50,91%</t>
+          <t>50,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>55,65%</t>
+          <t>55,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>735277</t>
+          <t>731937</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>818824</t>
+          <t>817205</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>41,86%</t>
+          <t>41,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,61%</t>
+          <t>46,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1758284</t>
+          <t>1756213</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1887994</t>
+          <t>1882024</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>47,29%</t>
+          <t>47,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>50,77%</t>
+          <t>50,61%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>473852</t>
+          <t>470622</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>551633</t>
+          <t>554061</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>437014</t>
+          <t>439052</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>512331</t>
+          <t>514636</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>929960</t>
+          <t>932435</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1036351</t>
+          <t>1039701</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>27,96%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>213032</t>
+          <t>217653</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>273162</t>
+          <t>270834</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>219577</t>
+          <t>220986</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>280556</t>
+          <t>282868</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>452606</t>
+          <t>455971</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>536526</t>
+          <t>543433</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,61%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>87409</t>
+          <t>87690</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>130699</t>
+          <t>130297</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>137427</t>
+          <t>138572</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>186706</t>
+          <t>187196</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>239162</t>
+          <t>239096</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>302218</t>
+          <t>303726</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4803,7 +4803,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,17%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>35116</t>
+          <t>37895</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>68233</t>
+          <t>68092</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>77372</t>
+          <t>78841</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>116449</t>
+          <t>118993</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>124265</t>
+          <t>122215</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>173166</t>
+          <t>174350</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,69%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>259245</t>
+          <t>256594</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>302024</t>
+          <t>303682</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>54,11%</t>
+          <t>53,56%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>63,04%</t>
+          <t>63,39%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>227419</t>
+          <t>227432</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>272366</t>
+          <t>273468</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>59,39%</t>
+          <t>59,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>498359</t>
+          <t>496582</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>560957</t>
+          <t>561915</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>53,15%</t>
+          <t>52,96%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>59,82%</t>
+          <t>59,92%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>92432</t>
+          <t>89453</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>130523</t>
+          <t>129800</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>105813</t>
+          <t>103745</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>145721</t>
+          <t>144721</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>206668</t>
+          <t>210051</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>263024</t>
+          <t>267018</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>28,48%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>40418</t>
+          <t>40833</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>69442</t>
+          <t>71318</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>33243</t>
+          <t>33190</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>58583</t>
+          <t>59662</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>79788</t>
+          <t>80622</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>120712</t>
+          <t>120776</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,88%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>15234</t>
+          <t>14281</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>35419</t>
+          <t>33676</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>19015</t>
+          <t>18558</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>39764</t>
+          <t>40037</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>38651</t>
+          <t>37379</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>67222</t>
+          <t>66765</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,12%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5715</t>
+          <t>5062</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>21904</t>
+          <t>22253</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5928</t>
+          <t>5626</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>19084</t>
+          <t>18407</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>14120</t>
+          <t>14145</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>35136</t>
+          <t>36179</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,86%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1723780</t>
+          <t>1719531</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1845324</t>
+          <t>1842436</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>50,54%</t>
+          <t>50,42%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>54,11%</t>
+          <t>54,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1500815</t>
+          <t>1504305</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1626575</t>
+          <t>1627381</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>42,25%</t>
+          <t>42,35%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>45,79%</t>
+          <t>45,81%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3261921</t>
+          <t>3262116</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3436495</t>
+          <t>3433162</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5828,7 +5828,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>49,36%</t>
+          <t>49,31%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>843332</t>
+          <t>847756</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>948068</t>
+          <t>952813</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>945634</t>
+          <t>948206</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1057551</t>
+          <t>1058633</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1816584</t>
+          <t>1832816</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1971612</t>
+          <t>1981169</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>28,45%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>410839</t>
+          <t>410905</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>496744</t>
+          <t>489517</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5984,7 +5984,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>460045</t>
+          <t>456587</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>547577</t>
+          <t>540856</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>891262</t>
+          <t>887785</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1005973</t>
+          <t>1011669</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,53%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>173255</t>
+          <t>172777</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>234473</t>
+          <t>229258</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>277228</t>
+          <t>278909</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>350629</t>
+          <t>352088</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>471465</t>
+          <t>471256</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>562939</t>
+          <t>562563</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6167,7 +6167,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,08%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>60849</t>
+          <t>60815</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>98979</t>
+          <t>100851</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6210,7 +6210,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>150488</t>
+          <t>150607</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>204243</t>
+          <t>203137</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6245,7 +6245,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>220440</t>
+          <t>224010</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>288648</t>
+          <t>286189</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,11%</t>
         </is>
       </c>
     </row>
@@ -6651,12 +6651,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>278470</t>
+          <t>277988</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>331099</t>
+          <t>329557</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6666,12 +6666,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>36,92%</t>
+          <t>36,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>43,89%</t>
+          <t>43,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6686,12 +6686,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>309445</t>
+          <t>306039</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>373187</t>
+          <t>369538</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,61%</t>
+          <t>37,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6721,12 +6721,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>604843</t>
+          <t>604081</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>686420</t>
+          <t>686470</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6736,7 +6736,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -6764,12 +6764,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>219412</t>
+          <t>218361</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>268847</t>
+          <t>268137</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6779,12 +6779,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>35,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6799,12 +6799,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>274709</t>
+          <t>274287</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>332915</t>
+          <t>334422</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>33,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>508331</t>
+          <t>505636</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>585643</t>
+          <t>586344</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>33,57%</t>
         </is>
       </c>
     </row>
@@ -6877,12 +6877,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>128031</t>
+          <t>129786</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>172984</t>
+          <t>172825</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6892,12 +6892,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>184914</t>
+          <t>183089</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>238309</t>
+          <t>237545</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>324020</t>
+          <t>328801</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>396618</t>
+          <t>395782</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,66%</t>
         </is>
       </c>
     </row>
@@ -6990,12 +6990,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>38824</t>
+          <t>38367</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>65073</t>
+          <t>63890</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7005,12 +7005,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>83012</t>
+          <t>84566</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>126269</t>
+          <t>125277</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7040,12 +7040,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>130456</t>
+          <t>129670</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>178711</t>
+          <t>178446</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7075,12 +7075,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,22%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2749</t>
+          <t>2992</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13503</t>
+          <t>13253</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>25932</t>
+          <t>26385</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>51121</t>
+          <t>50953</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>31308</t>
+          <t>30659</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>58424</t>
+          <t>57961</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,32%</t>
         </is>
       </c>
     </row>
@@ -7333,12 +7333,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>822811</t>
+          <t>824817</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>916027</t>
+          <t>911320</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7348,12 +7348,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>39,71%</t>
+          <t>39,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>44,21%</t>
+          <t>43,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7368,12 +7368,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>692574</t>
+          <t>694287</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>780629</t>
+          <t>780208</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7383,12 +7383,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>34,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,33%</t>
+          <t>39,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7403,12 +7403,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1537089</t>
+          <t>1542497</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1663782</t>
+          <t>1661631</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7418,12 +7418,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>37,89%</t>
+          <t>38,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>40,96%</t>
         </is>
       </c>
     </row>
@@ -7446,12 +7446,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>682213</t>
+          <t>685050</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>772832</t>
+          <t>767884</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>33,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>37,06%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>655630</t>
+          <t>655200</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>741466</t>
+          <t>742130</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7496,12 +7496,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>33,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,36%</t>
+          <t>37,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1363799</t>
+          <t>1369294</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1492464</t>
+          <t>1491554</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7531,12 +7531,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>33,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>36,79%</t>
+          <t>36,77%</t>
         </is>
       </c>
     </row>
@@ -7559,12 +7559,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>302013</t>
+          <t>303094</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>367311</t>
+          <t>370852</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7574,12 +7574,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>309928</t>
+          <t>308150</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>382506</t>
+          <t>378283</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>630757</t>
+          <t>627806</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>725971</t>
+          <t>724215</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,85%</t>
         </is>
       </c>
     </row>
@@ -7672,12 +7672,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>82704</t>
+          <t>81344</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>121767</t>
+          <t>121710</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7687,12 +7687,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7707,12 +7707,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>120819</t>
+          <t>118112</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>165378</t>
+          <t>164890</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7722,12 +7722,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7742,12 +7742,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>210827</t>
+          <t>212816</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>271643</t>
+          <t>271244</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,69%</t>
         </is>
       </c>
     </row>
@@ -7785,12 +7785,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>32475</t>
+          <t>32539</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>59871</t>
+          <t>59878</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7820,12 +7820,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>51475</t>
+          <t>51281</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>82951</t>
+          <t>81400</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7835,12 +7835,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>89518</t>
+          <t>92471</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>133924</t>
+          <t>132314</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,26%</t>
         </is>
       </c>
     </row>
@@ -8015,12 +8015,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>250981</t>
+          <t>250453</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>302839</t>
+          <t>301146</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8030,12 +8030,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>45,97%</t>
+          <t>45,87%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>55,46%</t>
+          <t>55,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8050,12 +8050,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>243089</t>
+          <t>244636</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>290499</t>
+          <t>292729</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8065,12 +8065,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>44,34%</t>
+          <t>44,62%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>52,99%</t>
+          <t>53,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>510523</t>
+          <t>508147</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>579176</t>
+          <t>577454</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>46,66%</t>
+          <t>46,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>52,93%</t>
+          <t>52,77%</t>
         </is>
       </c>
     </row>
@@ -8128,12 +8128,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>141013</t>
+          <t>140377</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>185333</t>
+          <t>185642</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8143,12 +8143,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8163,12 +8163,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>134137</t>
+          <t>133406</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>176290</t>
+          <t>173757</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8178,12 +8178,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>31,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8198,12 +8198,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>284342</t>
+          <t>287069</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>345868</t>
+          <t>349839</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>31,97%</t>
         </is>
       </c>
     </row>
@@ -8241,12 +8241,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>63902</t>
+          <t>63946</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>100488</t>
+          <t>98988</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8256,12 +8256,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8276,12 +8276,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>56974</t>
+          <t>55474</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>87967</t>
+          <t>90057</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8291,12 +8291,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8311,12 +8311,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>128751</t>
+          <t>128370</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>175665</t>
+          <t>178262</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8326,12 +8326,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,29%</t>
         </is>
       </c>
     </row>
@@ -8354,12 +8354,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11282</t>
+          <t>11341</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>28711</t>
+          <t>28949</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8369,12 +8369,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8389,12 +8389,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>21509</t>
+          <t>21701</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>45437</t>
+          <t>43964</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8404,12 +8404,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8424,12 +8424,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>37179</t>
+          <t>35255</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>65328</t>
+          <t>65963</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8439,12 +8439,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,03%</t>
         </is>
       </c>
     </row>
@@ -8467,12 +8467,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3031</t>
+          <t>3066</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>16460</t>
+          <t>17894</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8487,7 +8487,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8502,12 +8502,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>14755</t>
+          <t>15156</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>34877</t>
+          <t>35510</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8517,12 +8517,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8537,12 +8537,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>21146</t>
+          <t>21605</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>45403</t>
+          <t>46832</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8552,12 +8552,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,28%</t>
         </is>
       </c>
     </row>
@@ -8697,12 +8697,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1386447</t>
+          <t>1392754</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1505598</t>
+          <t>1502389</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8712,12 +8712,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>41,11%</t>
+          <t>41,3%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>44,65%</t>
+          <t>44,55%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8732,12 +8732,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1286393</t>
+          <t>1287276</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1403990</t>
+          <t>1407719</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8747,12 +8747,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>36,52%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>39,83%</t>
+          <t>39,93%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8767,12 +8767,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2709238</t>
+          <t>2710025</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2882479</t>
+          <t>2876953</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8782,12 +8782,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>39,28%</t>
+          <t>39,29%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>41,79%</t>
+          <t>41,71%</t>
         </is>
       </c>
     </row>
@@ -8810,12 +8810,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1077911</t>
+          <t>1082118</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1190259</t>
+          <t>1189301</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8825,12 +8825,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>35,3%</t>
+          <t>35,27%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8845,12 +8845,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1099022</t>
+          <t>1100965</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1212959</t>
+          <t>1211851</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8860,12 +8860,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>31,23%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>34,41%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8880,12 +8880,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2214990</t>
+          <t>2201171</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2376241</t>
+          <t>2365485</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8895,12 +8895,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>31,91%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>34,29%</t>
         </is>
       </c>
     </row>
@@ -8923,12 +8923,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>519376</t>
+          <t>521980</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>609599</t>
+          <t>611143</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8938,12 +8938,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8958,12 +8958,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>579528</t>
+          <t>576580</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>668805</t>
+          <t>674223</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8973,12 +8973,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8993,12 +8993,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1129556</t>
+          <t>1129582</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1258740</t>
+          <t>1264240</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9013,7 +9013,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,33%</t>
         </is>
       </c>
     </row>
@@ -9036,12 +9036,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>144798</t>
+          <t>145180</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>196975</t>
+          <t>195589</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9051,82 +9051,82 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
+          <t>5,8%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>274560</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>239650</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>308193</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>7,79%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>6,8%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>8,74%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>410</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>443299</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>402758</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>484283</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>6,43%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
           <t>5,84%</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>251</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>274560</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>240820</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>307298</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>7,79%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>6,83%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>8,72%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>410</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>443299</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>400420</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>482073</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>6,43%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>5,81%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,02%</t>
         </is>
       </c>
     </row>
@@ -9149,12 +9149,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>44743</t>
+          <t>44770</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>78047</t>
+          <t>76505</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9169,72 +9169,72 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
+          <t>2,27%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>125636</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>105309</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>152689</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>3,56%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>2,99%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>4,33%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>184804</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>159257</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>216324</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>2,68%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
           <t>2,31%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>125636</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>105430</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>148447</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>3,56%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>2,99%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>4,21%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>172</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>184804</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>159804</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>216735</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>2,68%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>2,32%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -9605,32 +9605,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>243646</t>
+          <t>271499</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>222271</t>
+          <t>250678</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>264880</t>
+          <t>295629</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>47,39%</t>
+          <t>47,0%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>43,23%</t>
+          <t>43,39%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>51,52%</t>
+          <t>51,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9640,32 +9640,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>323571</t>
+          <t>344572</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>302345</t>
+          <t>324503</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>342931</t>
+          <t>367556</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>43,03%</t>
+          <t>42,18%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>40,21%</t>
+          <t>39,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>45,6%</t>
+          <t>44,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9675,32 +9675,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>567218</t>
+          <t>616070</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>538952</t>
+          <t>585419</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>595537</t>
+          <t>650528</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>44,8%</t>
+          <t>44,17%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>42,57%</t>
+          <t>41,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>47,04%</t>
+          <t>46,64%</t>
         </is>
       </c>
     </row>
@@ -9718,32 +9718,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>139428</t>
+          <t>151360</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>122975</t>
+          <t>131162</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>161194</t>
+          <t>172897</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>29,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9753,32 +9753,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>207523</t>
+          <t>230598</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>189143</t>
+          <t>209661</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>226731</t>
+          <t>251180</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>30,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9788,32 +9788,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>346950</t>
+          <t>381957</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>320710</t>
+          <t>356075</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>372318</t>
+          <t>411540</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>29,51%</t>
         </is>
       </c>
     </row>
@@ -9831,32 +9831,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>76640</t>
+          <t>91579</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>63008</t>
+          <t>73548</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>92225</t>
+          <t>110249</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9866,32 +9866,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>124117</t>
+          <t>137735</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>107990</t>
+          <t>121420</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>139168</t>
+          <t>154862</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9901,32 +9901,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>200757</t>
+          <t>229313</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>181001</t>
+          <t>207551</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>223264</t>
+          <t>251028</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>18,0%</t>
         </is>
       </c>
     </row>
@@ -9944,32 +9944,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>34460</t>
+          <t>40201</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25885</t>
+          <t>30202</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>45848</t>
+          <t>53617</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9979,32 +9979,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>65412</t>
+          <t>72586</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>54878</t>
+          <t>61296</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>77667</t>
+          <t>85457</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10014,32 +10014,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>99872</t>
+          <t>112786</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>85428</t>
+          <t>97530</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>114141</t>
+          <t>130469</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,35%</t>
         </is>
       </c>
     </row>
@@ -10057,32 +10057,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>19965</t>
+          <t>23078</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12670</t>
+          <t>15197</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>28477</t>
+          <t>34161</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10092,32 +10092,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>31359</t>
+          <t>31471</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>22532</t>
+          <t>23423</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>53024</t>
+          <t>40992</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10127,32 +10127,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>51324</t>
+          <t>54549</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>40438</t>
+          <t>43775</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>68706</t>
+          <t>67951</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>4,87%</t>
         </is>
       </c>
     </row>
@@ -10170,17 +10170,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>514139</t>
+          <t>577716</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>514139</t>
+          <t>577716</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>514139</t>
+          <t>577716</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10205,17 +10205,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>751982</t>
+          <t>816961</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>751982</t>
+          <t>816961</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>751982</t>
+          <t>816961</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10240,17 +10240,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1266121</t>
+          <t>1394676</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1266121</t>
+          <t>1394676</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1266121</t>
+          <t>1394676</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10287,32 +10287,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1453837</t>
+          <t>1292475</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1334845</t>
+          <t>1238576</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1724382</t>
+          <t>1345383</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>63,64%</t>
+          <t>58,11%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>58,44%</t>
+          <t>55,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>75,49%</t>
+          <t>60,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10322,32 +10322,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1140868</t>
+          <t>1156677</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1082683</t>
+          <t>1114466</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1273329</t>
+          <t>1201429</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>56,21%</t>
+          <t>53,36%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>53,34%</t>
+          <t>51,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>62,74%</t>
+          <t>55,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10357,32 +10357,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>2594706</t>
+          <t>2449151</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2458415</t>
+          <t>2381869</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2927984</t>
+          <t>2519603</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>60,15%</t>
+          <t>55,77%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>56,99%</t>
+          <t>54,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>67,87%</t>
+          <t>57,37%</t>
         </is>
       </c>
     </row>
@@ -10400,32 +10400,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>529617</t>
+          <t>581766</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>374799</t>
+          <t>538187</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>612420</t>
+          <t>627793</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10435,32 +10435,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>547396</t>
+          <t>616896</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>479528</t>
+          <t>580517</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>591711</t>
+          <t>655240</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>30,23%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10470,32 +10470,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1077013</t>
+          <t>1198662</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>877542</t>
+          <t>1135370</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1170222</t>
+          <t>1256185</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>28,6%</t>
         </is>
       </c>
     </row>
@@ -10513,32 +10513,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>203579</t>
+          <t>232754</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>133076</t>
+          <t>198640</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>242044</t>
+          <t>263920</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10548,32 +10548,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>197921</t>
+          <t>221247</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>168058</t>
+          <t>197496</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>229905</t>
+          <t>248978</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10583,32 +10583,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>401500</t>
+          <t>454001</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>330345</t>
+          <t>412573</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>452714</t>
+          <t>497837</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>11,34%</t>
         </is>
       </c>
     </row>
@@ -10626,32 +10626,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>64326</t>
+          <t>78848</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>44345</t>
+          <t>62705</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>83424</t>
+          <t>97738</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
+          <t>3,54%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
           <t>2,82%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1,94%</t>
-        </is>
-      </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10661,32 +10661,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>100274</t>
+          <t>119660</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>83785</t>
+          <t>101650</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>119374</t>
+          <t>139795</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10696,32 +10696,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>164599</t>
+          <t>198508</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>134681</t>
+          <t>172607</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>191420</t>
+          <t>225630</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>5,14%</t>
         </is>
       </c>
     </row>
@@ -10739,32 +10739,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>32933</t>
+          <t>38424</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>21166</t>
+          <t>27770</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>45760</t>
+          <t>51415</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10774,32 +10774,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>43195</t>
+          <t>53034</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>32014</t>
+          <t>41795</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>57171</t>
+          <t>69659</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10809,32 +10809,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>76128</t>
+          <t>91458</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>59937</t>
+          <t>75413</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>94553</t>
+          <t>111643</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -10852,17 +10852,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2284292</t>
+          <t>2224267</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2284292</t>
+          <t>2224267</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2284292</t>
+          <t>2224267</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10887,17 +10887,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2029653</t>
+          <t>2167514</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2029653</t>
+          <t>2167514</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2029653</t>
+          <t>2167514</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10922,17 +10922,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>4313946</t>
+          <t>4391781</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>4313946</t>
+          <t>4391781</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>4313946</t>
+          <t>4391781</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10969,32 +10969,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>403012</t>
+          <t>439696</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>371637</t>
+          <t>412960</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>427785</t>
+          <t>465992</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>62,58%</t>
+          <t>62,15%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>57,71%</t>
+          <t>58,37%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>66,43%</t>
+          <t>65,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11004,32 +11004,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>399439</t>
+          <t>440824</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>375795</t>
+          <t>415860</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>419453</t>
+          <t>463921</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>60,54%</t>
+          <t>60,11%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>56,95%</t>
+          <t>56,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>63,57%</t>
+          <t>63,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11039,32 +11039,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>802452</t>
+          <t>880520</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>767735</t>
+          <t>845448</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>836528</t>
+          <t>913986</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>61,55%</t>
+          <t>61,11%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>58,88%</t>
+          <t>58,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>64,16%</t>
+          <t>63,43%</t>
         </is>
       </c>
     </row>
@@ -11082,32 +11082,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>163329</t>
+          <t>173719</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>139043</t>
+          <t>150554</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>193126</t>
+          <t>200228</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11117,32 +11117,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>171251</t>
+          <t>191876</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>153457</t>
+          <t>170987</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>190606</t>
+          <t>212672</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11152,32 +11152,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>334580</t>
+          <t>365596</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>304367</t>
+          <t>337468</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>369651</t>
+          <t>401518</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>27,87%</t>
         </is>
       </c>
     </row>
@@ -11195,32 +11195,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>43543</t>
+          <t>54207</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>32194</t>
+          <t>41555</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>57415</t>
+          <t>73738</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11230,32 +11230,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>43738</t>
+          <t>49725</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>32275</t>
+          <t>38067</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>56312</t>
+          <t>63115</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11265,32 +11265,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>87280</t>
+          <t>103932</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>70828</t>
+          <t>86911</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>106911</t>
+          <t>126088</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,75%</t>
         </is>
       </c>
     </row>
@@ -11308,32 +11308,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>22239</t>
+          <t>26518</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14499</t>
+          <t>18000</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>35999</t>
+          <t>40235</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11343,32 +11343,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>31484</t>
+          <t>35739</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>23727</t>
+          <t>27341</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>42807</t>
+          <t>46172</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11378,32 +11378,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>53723</t>
+          <t>62257</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>41885</t>
+          <t>49095</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>69011</t>
+          <t>78726</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,46%</t>
         </is>
       </c>
     </row>
@@ -11421,32 +11421,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>11865</t>
+          <t>13362</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6251</t>
+          <t>7075</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>20883</t>
+          <t>22995</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11456,67 +11456,67 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>13922</t>
+          <t>15243</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>9036</t>
+          <t>9955</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>21224</t>
+          <t>22412</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
+          <t>1,36%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>3,06%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>28604</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>19768</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>39802</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>1,99%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
           <t>1,37%</t>
         </is>
       </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>3,22%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>25787</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>18327</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>37471</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>1,98%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>1,41%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -11534,17 +11534,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>643988</t>
+          <t>707502</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>643988</t>
+          <t>707502</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>643988</t>
+          <t>707502</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11569,17 +11569,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>659834</t>
+          <t>733407</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>659834</t>
+          <t>733407</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>659834</t>
+          <t>733407</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11604,17 +11604,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1303823</t>
+          <t>1440909</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1303823</t>
+          <t>1440909</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1303823</t>
+          <t>1440909</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11651,32 +11651,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>2100496</t>
+          <t>2003668</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1978965</t>
+          <t>1935850</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2428180</t>
+          <t>2070093</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>61,02%</t>
+          <t>57,09%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>57,49%</t>
+          <t>55,16%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>70,54%</t>
+          <t>58,99%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11686,32 +11686,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1863879</t>
+          <t>1942072</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1793211</t>
+          <t>1886304</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1966539</t>
+          <t>1996017</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>54,16%</t>
+          <t>52,24%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>52,11%</t>
+          <t>50,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>57,14%</t>
+          <t>53,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11721,32 +11721,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>3964375</t>
+          <t>3945741</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3814007</t>
+          <t>3856662</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4329830</t>
+          <t>4025439</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>57,59%</t>
+          <t>54,59%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>55,4%</t>
+          <t>53,36%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>62,9%</t>
+          <t>55,7%</t>
         </is>
       </c>
     </row>
@@ -11764,32 +11764,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>832374</t>
+          <t>906845</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>620898</t>
+          <t>848923</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>913009</t>
+          <t>964036</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11799,32 +11799,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>926169</t>
+          <t>1039370</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>862111</t>
+          <t>991539</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>982123</t>
+          <t>1092067</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11834,32 +11834,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1758543</t>
+          <t>1946215</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1549167</t>
+          <t>1873490</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1866922</t>
+          <t>2018587</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>27,93%</t>
         </is>
       </c>
     </row>
@@ -11877,32 +11877,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>323761</t>
+          <t>378540</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>251584</t>
+          <t>337323</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>367073</t>
+          <t>419402</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11912,32 +11912,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>365775</t>
+          <t>408707</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>327232</t>
+          <t>377794</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>402257</t>
+          <t>442156</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11947,32 +11947,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>689537</t>
+          <t>787247</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>605503</t>
+          <t>735380</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>747587</t>
+          <t>845833</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>11,7%</t>
         </is>
       </c>
     </row>
@@ -11990,32 +11990,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>121025</t>
+          <t>145567</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>93912</t>
+          <t>123771</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>143740</t>
+          <t>171399</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12025,32 +12025,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>197170</t>
+          <t>227985</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>176020</t>
+          <t>204989</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>220811</t>
+          <t>254399</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12060,32 +12060,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>318194</t>
+          <t>373552</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>273990</t>
+          <t>339292</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>352472</t>
+          <t>407597</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,64%</t>
         </is>
       </c>
     </row>
@@ -12103,32 +12103,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>64763</t>
+          <t>74864</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>47549</t>
+          <t>60297</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>83040</t>
+          <t>93511</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12138,32 +12138,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>88476</t>
+          <t>99747</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>73517</t>
+          <t>83683</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>112631</t>
+          <t>118788</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12173,32 +12173,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>153240</t>
+          <t>174611</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>128892</t>
+          <t>151515</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>181378</t>
+          <t>200033</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -12216,17 +12216,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3442419</t>
+          <t>3509484</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3442419</t>
+          <t>3509484</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3442419</t>
+          <t>3509484</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12251,17 +12251,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3441470</t>
+          <t>3717881</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3441470</t>
+          <t>3717881</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3441470</t>
+          <t>3717881</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12286,17 +12286,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>6883889</t>
+          <t>7227366</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>6883889</t>
+          <t>7227366</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>6883889</t>
+          <t>7227366</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
